--- a/SGC-CKN/Excel/2d3b3213-05da-4777-8175-5e5cf61349a5_Đường_kính_D800_P11_94_D800_06-04-2026.xlsx
+++ b/SGC-CKN/Excel/2d3b3213-05da-4777-8175-5e5cf61349a5_Đường_kính_D800_P11_94_D800_06-04-2026.xlsx
@@ -95,7 +95,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>Sét pha, xám nâu, TT dẻo mềm</t>
+    <t>Sét pha, xám xanh, xám đen, xám nâu, xám ghi, TT dẻo mềm</t>
   </si>
   <si>
     <t xml:space="preserve">11:00
@@ -112,7 +112,7 @@
     <t>2</t>
   </si>
   <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen, xám trắng, xám xanh TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">12:00
@@ -125,7 +125,7 @@
     <t>3</t>
   </si>
   <si>
-    <t>Sét- đôi chỗ kẹp cát pha, lẫn dăm sạn TT dẻo mềm</t>
+    <t>Sét, đôi chỗ kẹp cát pha, lẫn dăm sạn, TT dẻo mềm</t>
   </si>
   <si>
     <t xml:space="preserve">13:00
@@ -135,7 +135,7 @@
     <t>4</t>
   </si>
   <si>
-    <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
+    <t>Sét xám vàng, nâu vàng, xám xanh, TT nửa cứng</t>
   </si>
   <si>
     <t xml:space="preserve">14:00
@@ -145,7 +145,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>Sét pha, xám xanh, xám ghi, TT dẻo mềm lẫn hữu cơ, kẹp cát</t>
+    <t>Sét pha - cát pha màu xám xanh, xám ghi, lẫn hữu cơ màu xám đen, trạng thái dẻo mềm</t>
   </si>
   <si>
     <t xml:space="preserve">14:30
@@ -155,7 +155,7 @@
     <t>6</t>
   </si>
   <si>
-    <t>Cát pha, xám vàng, xám ghi TT dẻo</t>
+    <t>Cát pha, xám ghi, xám nâu, xám vàng, TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">15:00
@@ -165,7 +165,7 @@
     <t>7</t>
   </si>
   <si>
-    <t>Cát thô vừa, KC chặt vừa lẫn sỏi sạn, có chỗ là hạt cát nhỏ bụi</t>
+    <t>Cát thô vừa, xám vàng, xám xanh, TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
     <t xml:space="preserve">15:36
@@ -178,7 +178,7 @@
     <t>8</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">17:00
@@ -1154,7 +1154,7 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-1.01</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
         <v>-3.66</v>
@@ -1163,10 +1163,10 @@
         <v>0.5</v>
       </c>
       <c r="I11" s="5">
-        <v>2.65</v>
+        <v>3.66</v>
       </c>
       <c r="J11" s="8">
-        <v>5.3</v>
+        <v>7.32</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1566,7 +1566,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-1.01</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
         <v>-3.66</v>
@@ -1575,10 +1575,10 @@
         <v>0.5</v>
       </c>
       <c r="H2" s="5">
-        <v>2.65</v>
+        <v>3.66</v>
       </c>
       <c r="I2" s="8">
-        <v>5.3</v>
+        <v>7.32</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1798,7 +1798,7 @@
         <v>8</v>
       </c>
       <c r="E10" s="33">
-        <v>-1.01</v>
+        <v>0</v>
       </c>
       <c r="F10" s="33">
         <v>-49.72</v>
@@ -1807,10 +1807,10 @@
         <v>6</v>
       </c>
       <c r="H10" s="33">
-        <v>48.71</v>
+        <v>49.72</v>
       </c>
       <c r="I10" s="33">
-        <v>8.12</v>
+        <v>8.29</v>
       </c>
     </row>
   </sheetData>
